--- a/040-進捗管理/052-バグ管理票_テンプレート.xlsx
+++ b/040-進捗管理/052-バグ管理票_テンプレート.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryomiyashita\Desktop\03_システム開発体験\090_模範解答\050-進捗管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\040-進捗管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A00715-4110-449C-ACD8-5BBA33272532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12216"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="問題点一覧" sheetId="7" r:id="rId1"/>
@@ -25,12 +26,12 @@
     <definedName name="工程" localSheetId="0">#REF!</definedName>
     <definedName name="工程">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913" concurrentManualCount="2"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="269">
   <si>
     <t>状態</t>
     <rPh sb="0" eb="2">
@@ -3248,11 +3249,382 @@
     <t>テストNo</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>SQL文に誤字があった</t>
+    <rPh sb="3" eb="4">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゴジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>鈴木崇志</t>
+    <rPh sb="0" eb="4">
+      <t>スズキタカユキ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ItemsDAOクラスの単体試験において以下のようなエラー文が表示された。
+列"cotegory_name"は存在しません
+＜問題点＞
+findAllメソッドで検索結果が取得できない</t>
+    <rPh sb="12" eb="16">
+      <t>タンタイシケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="63" eb="66">
+      <t>モンダイテン</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>SQL文の誤字を修正</t>
+    <rPh sb="3" eb="4">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゴジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>メイン画面から商品検索結果画面へ遷移すると500番エラー"サーブレットクラスを初期化中にエラーが発生しました"と表示される。
+＜問題点＞
+メイン画面から商品検索結果画面へ遷移できない</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="13">
+      <t>ショウヒンケンサクケッカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>ショキカチュウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>モンダイテン</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="76" eb="84">
+      <t>ショウヒンケンサクケッカガメン</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>SearchResultServletクラスに引数無しのコンストラクタを定義していないため</t>
+    <rPh sb="23" eb="26">
+      <t>ヒキスウナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>1. もともと実装していた引数ありのコンストラクタを削除
+2. デフォルトコンストラクタを明記
+3. SearchResultServletにinitメソッドを実装
+ 　initメソッドでフィールドの初期化
+4. 新たにクラスを作成し、SearchResultServiceクラスをインスタンス化しインスタンスを渡す</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>メイキ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="100" eb="103">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="156" eb="157">
+      <t>ワタ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>001</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>クラス図</t>
+    <rPh sb="3" eb="4">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>SearchResultServletクラス、ItemDetailServletクラスの属性 と操作</t>
+    <rPh sb="44" eb="46">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>1. 属性からfinal修飾子を削除
+2. 引数ありのコンストラクタを削除</t>
+    <rPh sb="3" eb="5">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>シュウショクシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒキスウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>鈴木崇志</t>
+    <rPh sb="0" eb="4">
+      <t>スズキタカユキ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>002</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>クラス仕様書</t>
+    <rPh sb="3" eb="6">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>処理4. 及び処理5. の削除</t>
+    <rPh sb="0" eb="2">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>MainServletのメソッド仕様書(init)</t>
+    <rPh sb="16" eb="19">
+      <t>シヨウショ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>SearchResultServletのクラス仕様、メソッド仕様(init)</t>
+    <rPh sb="23" eb="25">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>1. クラス仕様において、iSearchResultServiceの種類を「-」に変更
+2. メソッド仕様(SearchResultServlet)をデフォルトコンストラクタに変更
+3. メソッド仕様(init)の追加</t>
+    <rPh sb="6" eb="8">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>GetInstanceContextListenerクラスのクラス仕様書を作成</t>
+    <rPh sb="33" eb="36">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>003</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>004</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>001
+002
+003
+004</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>サーブレットに関する知識不足</t>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>チシキブソク</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>サーブレットに関する知識をより学習して身に着ける</t>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>ecsite</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>次へのリンクを押しても画面遷移しない</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
+  <si>
+    <t>${currentPage + 1}のとこを誤字してた
+curretnPsge</t>
+    <rPh sb="22" eb="24">
+      <t>ゴジ</t>
+    </rPh>
+    <phoneticPr fontId="6"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
@@ -3406,7 +3778,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3492,6 +3864,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7983,6 +8364,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -8018,6 +8416,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -8193,18 +8608,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="10" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" style="19" customWidth="1"/>
     <col min="2" max="2" width="6.33203125" style="13" customWidth="1"/>
     <col min="3" max="3" width="26.109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" style="10" customWidth="1"/>
     <col min="7" max="7" width="36.6640625" style="10" customWidth="1"/>
     <col min="8" max="8" width="38.6640625" style="10" customWidth="1"/>
@@ -8220,12 +8635,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:18" s="14" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
@@ -8237,7 +8654,7 @@
       <c r="C2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="31" t="s">
         <v>237</v>
       </c>
       <c r="E2" s="17" t="s">
@@ -8284,53 +8701,117 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="93.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" s="12">
+        <v>45583</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="I3" s="2"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="4"/>
+      <c r="J3" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K3" s="12">
+        <v>45583</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>227</v>
+      </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="12"/>
+      <c r="A4" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="12">
+        <v>45581</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="12">
+        <v>45581</v>
+      </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="4"/>
+      <c r="M4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>229</v>
+      </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="Q4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="8"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="8"/>
@@ -8344,10 +8825,10 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="8"/>
       <c r="F6" s="12"/>
       <c r="G6" s="2"/>
@@ -8364,10 +8845,10 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="4"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="8"/>
       <c r="F7" s="12"/>
       <c r="G7" s="2"/>
@@ -8384,10 +8865,10 @@
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="4"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="8"/>
       <c r="F8" s="12"/>
       <c r="G8" s="2"/>
@@ -8404,10 +8885,10 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="4"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="8"/>
       <c r="F9" s="12"/>
       <c r="G9" s="2"/>
@@ -8424,10 +8905,10 @@
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="8"/>
       <c r="F10" s="12"/>
       <c r="G10" s="2"/>
@@ -8444,10 +8925,10 @@
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="4"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="8"/>
       <c r="F11" s="12"/>
       <c r="G11" s="2"/>
@@ -8464,10 +8945,10 @@
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="8"/>
       <c r="F12" s="12"/>
       <c r="G12" s="2"/>
@@ -8484,10 +8965,10 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="4"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="D13" s="4"/>
       <c r="E13" s="8"/>
       <c r="F13" s="12"/>
       <c r="G13" s="2"/>
@@ -8504,10 +8985,10 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="D14" s="4"/>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
       <c r="G14" s="2"/>
@@ -8524,10 +9005,10 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="D15" s="4"/>
       <c r="E15" s="8"/>
       <c r="F15" s="12"/>
       <c r="G15" s="2"/>
@@ -8544,10 +9025,10 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="4"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="D16" s="4"/>
       <c r="E16" s="8"/>
       <c r="F16" s="12"/>
       <c r="G16" s="2"/>
@@ -8564,10 +9045,10 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
+      <c r="A17" s="29"/>
       <c r="B17" s="4"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="8"/>
       <c r="F17" s="12"/>
       <c r="G17" s="2"/>
@@ -8584,10 +9065,10 @@
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="4"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="8"/>
       <c r="F18" s="12"/>
       <c r="G18" s="2"/>
@@ -8604,10 +9085,10 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="4"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="D19" s="4"/>
       <c r="E19" s="8"/>
       <c r="F19" s="12"/>
       <c r="G19" s="2"/>
@@ -8624,10 +9105,10 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="D20" s="4"/>
       <c r="E20" s="8"/>
       <c r="F20" s="12"/>
       <c r="G20" s="2"/>
@@ -8644,10 +9125,10 @@
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="4"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="D21" s="4"/>
       <c r="E21" s="8"/>
       <c r="F21" s="12"/>
       <c r="G21" s="2"/>
@@ -8664,10 +9145,10 @@
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="D22" s="4"/>
       <c r="E22" s="8"/>
       <c r="F22" s="12"/>
       <c r="G22" s="2"/>
@@ -8684,10 +9165,10 @@
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="4"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="D23" s="4"/>
       <c r="E23" s="8"/>
       <c r="F23" s="12"/>
       <c r="G23" s="2"/>
@@ -8704,10 +9185,10 @@
       <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="4"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="D24" s="4"/>
       <c r="E24" s="8"/>
       <c r="F24" s="12"/>
       <c r="G24" s="2"/>
@@ -8724,10 +9205,10 @@
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="4"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="8"/>
       <c r="F25" s="12"/>
       <c r="G25" s="2"/>
@@ -8744,10 +9225,10 @@
       <c r="R25" s="2"/>
     </row>
     <row r="26" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="4"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="8"/>
       <c r="F26" s="12"/>
       <c r="G26" s="2"/>
@@ -8764,10 +9245,10 @@
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="4"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="8"/>
       <c r="F27" s="12"/>
       <c r="G27" s="2"/>
@@ -8784,10 +9265,10 @@
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="4"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="8"/>
       <c r="F28" s="12"/>
       <c r="G28" s="2"/>
@@ -8804,10 +9285,10 @@
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="4"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="D29" s="4"/>
       <c r="E29" s="8"/>
       <c r="F29" s="12"/>
       <c r="G29" s="2"/>
@@ -8824,10 +9305,10 @@
       <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="4"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="D30" s="4"/>
       <c r="E30" s="8"/>
       <c r="F30" s="12"/>
       <c r="G30" s="2"/>
@@ -8844,10 +9325,10 @@
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="4"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="D31" s="4"/>
       <c r="E31" s="8"/>
       <c r="F31" s="12"/>
       <c r="G31" s="2"/>
@@ -8864,10 +9345,10 @@
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="4"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="8"/>
       <c r="F32" s="12"/>
       <c r="G32" s="2"/>
@@ -8884,10 +9365,10 @@
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="4"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="D33" s="4"/>
       <c r="E33" s="8"/>
       <c r="F33" s="12"/>
       <c r="G33" s="2"/>
@@ -8904,10 +9385,10 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="4"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="D34" s="4"/>
       <c r="E34" s="8"/>
       <c r="F34" s="12"/>
       <c r="G34" s="2"/>
@@ -8924,10 +9405,10 @@
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="4"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="8"/>
       <c r="F35" s="12"/>
       <c r="G35" s="2"/>
@@ -8944,10 +9425,10 @@
       <c r="R35" s="2"/>
     </row>
     <row r="36" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="4"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="8"/>
       <c r="F36" s="12"/>
       <c r="G36" s="2"/>
@@ -8964,10 +9445,10 @@
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="4"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="8"/>
       <c r="F37" s="12"/>
       <c r="G37" s="2"/>
@@ -8984,10 +9465,10 @@
       <c r="R37" s="2"/>
     </row>
     <row r="38" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="4"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="D38" s="4"/>
       <c r="E38" s="8"/>
       <c r="F38" s="12"/>
       <c r="G38" s="2"/>
@@ -9004,10 +9485,10 @@
       <c r="R38" s="2"/>
     </row>
     <row r="39" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="8"/>
       <c r="F39" s="12"/>
       <c r="G39" s="2"/>
@@ -9024,10 +9505,10 @@
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="4"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
+      <c r="D40" s="4"/>
       <c r="E40" s="8"/>
       <c r="F40" s="12"/>
       <c r="G40" s="2"/>
@@ -9044,10 +9525,10 @@
       <c r="R40" s="2"/>
     </row>
     <row r="41" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="4"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="D41" s="4"/>
       <c r="E41" s="8"/>
       <c r="F41" s="12"/>
       <c r="G41" s="2"/>
@@ -9064,10 +9545,10 @@
       <c r="R41" s="2"/>
     </row>
     <row r="42" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="4"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="D42" s="4"/>
       <c r="E42" s="8"/>
       <c r="F42" s="12"/>
       <c r="G42" s="2"/>
@@ -9084,10 +9565,10 @@
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="4"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="D43" s="4"/>
       <c r="E43" s="8"/>
       <c r="F43" s="12"/>
       <c r="G43" s="2"/>
@@ -9104,10 +9585,10 @@
       <c r="R43" s="2"/>
     </row>
     <row r="44" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="4"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="8"/>
       <c r="F44" s="12"/>
       <c r="G44" s="2"/>
@@ -9124,10 +9605,10 @@
       <c r="R44" s="2"/>
     </row>
     <row r="45" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="4"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="D45" s="4"/>
       <c r="E45" s="8"/>
       <c r="F45" s="12"/>
       <c r="G45" s="2"/>
@@ -9144,10 +9625,10 @@
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
+      <c r="A46" s="29"/>
       <c r="B46" s="4"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="D46" s="4"/>
       <c r="E46" s="8"/>
       <c r="F46" s="12"/>
       <c r="G46" s="2"/>
@@ -9164,10 +9645,10 @@
       <c r="R46" s="2"/>
     </row>
     <row r="47" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="4"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="D47" s="4"/>
       <c r="E47" s="8"/>
       <c r="F47" s="12"/>
       <c r="G47" s="2"/>
@@ -9184,10 +9665,10 @@
       <c r="R47" s="2"/>
     </row>
     <row r="48" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
+      <c r="A48" s="29"/>
       <c r="B48" s="4"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="D48" s="4"/>
       <c r="E48" s="8"/>
       <c r="F48" s="12"/>
       <c r="G48" s="2"/>
@@ -9204,10 +9685,10 @@
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
+      <c r="A49" s="29"/>
       <c r="B49" s="4"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="8"/>
       <c r="F49" s="12"/>
       <c r="G49" s="2"/>
@@ -9224,10 +9705,10 @@
       <c r="R49" s="2"/>
     </row>
     <row r="50" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
+      <c r="A50" s="29"/>
       <c r="B50" s="4"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="8"/>
       <c r="F50" s="12"/>
       <c r="G50" s="2"/>
@@ -9244,10 +9725,10 @@
       <c r="R50" s="2"/>
     </row>
     <row r="51" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
+      <c r="A51" s="29"/>
       <c r="B51" s="4"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="D51" s="4"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12"/>
       <c r="G51" s="2"/>
@@ -9264,10 +9745,10 @@
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="4"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="D52" s="4"/>
       <c r="E52" s="8"/>
       <c r="F52" s="12"/>
       <c r="G52" s="2"/>
@@ -9284,10 +9765,10 @@
       <c r="R52" s="2"/>
     </row>
     <row r="53" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
+      <c r="A53" s="29"/>
       <c r="B53" s="4"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="D53" s="4"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12"/>
       <c r="G53" s="2"/>
@@ -9304,10 +9785,10 @@
       <c r="R53" s="2"/>
     </row>
     <row r="54" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
+      <c r="A54" s="29"/>
       <c r="B54" s="4"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="D54" s="4"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12"/>
       <c r="G54" s="2"/>
@@ -9324,10 +9805,10 @@
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
+      <c r="A55" s="29"/>
       <c r="B55" s="4"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="D55" s="4"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12"/>
       <c r="G55" s="2"/>
@@ -9344,10 +9825,10 @@
       <c r="R55" s="2"/>
     </row>
     <row r="56" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
+      <c r="A56" s="29"/>
       <c r="B56" s="4"/>
       <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="D56" s="4"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12"/>
       <c r="G56" s="2"/>
@@ -9364,10 +9845,10 @@
       <c r="R56" s="2"/>
     </row>
     <row r="57" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
+      <c r="A57" s="29"/>
       <c r="B57" s="4"/>
       <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="D57" s="4"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12"/>
       <c r="G57" s="2"/>
@@ -9384,10 +9865,10 @@
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
+      <c r="A58" s="29"/>
       <c r="B58" s="4"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="D58" s="4"/>
       <c r="E58" s="8"/>
       <c r="F58" s="12"/>
       <c r="G58" s="2"/>
@@ -9404,10 +9885,10 @@
       <c r="R58" s="2"/>
     </row>
     <row r="59" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="4"/>
       <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+      <c r="D59" s="4"/>
       <c r="E59" s="8"/>
       <c r="F59" s="12"/>
       <c r="G59" s="2"/>
@@ -9424,10 +9905,10 @@
       <c r="R59" s="2"/>
     </row>
     <row r="60" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
+      <c r="A60" s="29"/>
       <c r="B60" s="4"/>
       <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="D60" s="4"/>
       <c r="E60" s="8"/>
       <c r="F60" s="12"/>
       <c r="G60" s="2"/>
@@ -9444,10 +9925,10 @@
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
+      <c r="A61" s="29"/>
       <c r="B61" s="4"/>
       <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="D61" s="4"/>
       <c r="E61" s="8"/>
       <c r="F61" s="12"/>
       <c r="G61" s="2"/>
@@ -9464,10 +9945,10 @@
       <c r="R61" s="2"/>
     </row>
     <row r="62" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
+      <c r="A62" s="29"/>
       <c r="B62" s="4"/>
       <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="D62" s="4"/>
       <c r="E62" s="8"/>
       <c r="F62" s="12"/>
       <c r="G62" s="2"/>
@@ -9484,10 +9965,10 @@
       <c r="R62" s="2"/>
     </row>
     <row r="63" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
+      <c r="A63" s="29"/>
       <c r="B63" s="4"/>
       <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="D63" s="4"/>
       <c r="E63" s="8"/>
       <c r="F63" s="12"/>
       <c r="G63" s="2"/>
@@ -9504,10 +9985,10 @@
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
+      <c r="A64" s="29"/>
       <c r="B64" s="4"/>
       <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="D64" s="4"/>
       <c r="E64" s="8"/>
       <c r="F64" s="12"/>
       <c r="G64" s="2"/>
@@ -9524,10 +10005,10 @@
       <c r="R64" s="2"/>
     </row>
     <row r="65" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
+      <c r="A65" s="29"/>
       <c r="B65" s="4"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
+      <c r="D65" s="4"/>
       <c r="E65" s="8"/>
       <c r="F65" s="12"/>
       <c r="G65" s="2"/>
@@ -9544,10 +10025,10 @@
       <c r="R65" s="2"/>
     </row>
     <row r="66" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="11"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="4"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
+      <c r="D66" s="4"/>
       <c r="E66" s="8"/>
       <c r="F66" s="12"/>
       <c r="G66" s="2"/>
@@ -9564,10 +10045,10 @@
       <c r="R66" s="2"/>
     </row>
     <row r="67" spans="1:18" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="11"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="4"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
+      <c r="D67" s="4"/>
       <c r="E67" s="8"/>
       <c r="F67" s="12"/>
       <c r="G67" s="2"/>
@@ -9584,10 +10065,10 @@
       <c r="R67" s="2"/>
     </row>
     <row r="68" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="11"/>
+      <c r="A68" s="29"/>
       <c r="B68" s="4"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+      <c r="D68" s="4"/>
       <c r="E68" s="8"/>
       <c r="F68" s="12"/>
       <c r="G68" s="2"/>
@@ -11356,22 +11837,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B68" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$B$70:$B$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P68" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$P$69:$P$71</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M68" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$M$69:$M$72</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L68" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>$L$69:$L$72</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N68" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>$N$69:$N$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O68">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O68" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$O$69:$O$72</formula1>
     </dataValidation>
   </dataValidations>
@@ -11381,7 +11862,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
@@ -11389,7 +11870,7 @@
     <col min="2" max="2" width="13.33203125" style="10" customWidth="1"/>
     <col min="3" max="3" width="15.44140625" style="10" customWidth="1"/>
     <col min="4" max="4" width="32.77734375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
@@ -11424,40 +11905,88 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="11"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="8"/>
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="12">
+        <v>45583</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="8"/>
+    <row r="4" spans="1:7" ht="24" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="12">
+        <v>45583</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="8"/>
+    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" s="12">
+        <v>45583</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="8"/>
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="12">
+        <v>45583</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -11612,7 +12141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11639,10 +12168,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="32"/>
       <c r="C1" s="8"/>
       <c r="D1" s="9"/>
     </row>
@@ -13264,65 +13793,62 @@
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:O11 O13:O18">
+  <dataValidations count="19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:O11 O13:O18" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>IF($L4=$L$33,$O$33,IF($L4=$L$34,$O$34:$O$34,IF($L4=$L$35,$O$35:$O$36,IF($L4=$L$36,$O$37:$O$38))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3 O12 O23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3 O12 O23" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>IF($L3=$L$34,$O$34:$O$34,IF($L3=$L$35,$O$34:$O$35,IF($L3=$L$36,$O$36:$O$38)))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L4:L12" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$33:$L$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M18 M23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M18 M23:M32" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>$M$34:$M$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P18 P23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P18 P23" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>$P$33:$P$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B23">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B18 B23" xr:uid="{00000000-0002-0000-0200-000005000000}">
       <formula1>$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N23 N3:N18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N23 N3:N18" xr:uid="{00000000-0002-0000-0200-000006000000}">
       <formula1>$N$33:$N$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N19:N22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N19:N22" xr:uid="{00000000-0002-0000-0200-000007000000}">
       <formula1>IF($M19=$M$31,$N$31:$N$36,IF($M19=$M$32,$N$31:$N$36,IF($M19=$M$33,$N$37:$N$38)))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19:B22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19:B22" xr:uid="{00000000-0002-0000-0200-000008000000}">
       <formula1>$B$32:$B$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P19:P22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P19:P22" xr:uid="{00000000-0002-0000-0200-000009000000}">
       <formula1>$P$31:$P$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M19:M22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M19:M22" xr:uid="{00000000-0002-0000-0200-00000A000000}">
       <formula1>$M$31:$M$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:L22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:L22" xr:uid="{00000000-0002-0000-0200-00000B000000}">
       <formula1>$L$31:$L$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O19:O22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O19:O22" xr:uid="{00000000-0002-0000-0200-00000C000000}">
       <formula1>IF($L19=$L$31,$O$31,IF($L19=$L$32,$O$32:$O$32,IF($L19=$L$33,$O$33:$O$34,IF($L19=$L$34,$O$35:$O$36))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N24:N32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N24:N32" xr:uid="{00000000-0002-0000-0200-00000D000000}">
       <formula1>IF($M24=$M$34,$N$34:$N$39,IF($M24=$M$35,$N$34:$N$39,IF($M24=$M$36,$N$40:$N$41)))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24:B32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B24:B32" xr:uid="{00000000-0002-0000-0200-00000E000000}">
       <formula1>$B$35:$B$38</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P24:P32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P24:P32" xr:uid="{00000000-0002-0000-0200-00000F000000}">
       <formula1>$P$34:$P$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M24:M32">
-      <formula1>$M$34:$M$36</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L23:L32 L13:L19 L3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L23:L32 L13:L19 L3" xr:uid="{00000000-0002-0000-0200-000011000000}">
       <formula1>$L$34:$L$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O24:O25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O24:O25" xr:uid="{00000000-0002-0000-0200-000012000000}">
       <formula1>IF($L24=$L$35,$O$35:$O$35,IF($L24=$L$36,$O$35:$O$36,IF($L24=$L$37,$O$37:$O$39)))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O26:O32">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O26:O32" xr:uid="{00000000-0002-0000-0200-000013000000}">
       <formula1>IF($L26=$L$34,$O$34,IF($L26=$L$35,$O$35:$O$35,IF($L26=$L$36,$O$36:$O$37,IF($L26=$L$37,$O$38:$O$39))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -13332,7 +13858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
